--- a/artfynd/A 17912-2025 artfynd.xlsx
+++ b/artfynd/A 17912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97365552</v>
+        <v>97365561</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551918.2005785239</v>
+        <v>551920</v>
       </c>
       <c r="R2" t="n">
-        <v>6992669.109541805</v>
+        <v>6992681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97365561</v>
+        <v>97365547</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551920.2751287563</v>
+        <v>551881</v>
       </c>
       <c r="R3" t="n">
-        <v>6992681.38809238</v>
+        <v>6992637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +844,9 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97365545</v>
+        <v>97365552</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551985.7382487882</v>
+        <v>551918</v>
       </c>
       <c r="R4" t="n">
-        <v>6992734.137375652</v>
+        <v>6992670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,21 +945,11 @@
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,6 +958,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,6 +976,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97365545</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>551986</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6992734</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>

--- a/artfynd/A 17912-2025 artfynd.xlsx
+++ b/artfynd/A 17912-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,8 +1101,19 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97365545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>